--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N94_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N94_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>15.94791406993771</v>
+        <v>2.591536036364877</v>
       </c>
       <c r="D2" t="n">
-        <v>3.277630995644969</v>
+        <v>0.5326150367923075</v>
       </c>
       <c r="E2" t="n">
-        <v>9.115993504248458</v>
+        <v>1.481348944440375</v>
       </c>
       <c r="F2" t="n">
-        <v>12.24767510780529</v>
+        <v>1.99024720501836</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>12.29057775443247</v>
+        <v>1.997218885095276</v>
       </c>
       <c r="D3" t="n">
-        <v>31.06066642109645</v>
+        <v>5.047358293428174</v>
       </c>
       <c r="E3" t="n">
-        <v>9.115993504248458</v>
+        <v>1.481348944440375</v>
       </c>
       <c r="F3" t="n">
-        <v>12.24767510780529</v>
+        <v>1.99024720501836</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.81615039714531</v>
+        <v>5.170124439536113</v>
       </c>
       <c r="D4" t="n">
-        <v>27.15237035241148</v>
+        <v>4.412260182266865</v>
       </c>
       <c r="E4" t="n">
-        <v>9.115993504248458</v>
+        <v>1.481348944440375</v>
       </c>
       <c r="F4" t="n">
-        <v>12.24767510780529</v>
+        <v>1.99024720501836</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>19.81167912744358</v>
+        <v>3.219397858209582</v>
       </c>
       <c r="D5" t="n">
-        <v>30.00629819225507</v>
+        <v>4.87602345624145</v>
       </c>
       <c r="E5" t="n">
-        <v>9.115993504248458</v>
+        <v>1.481348944440375</v>
       </c>
       <c r="F5" t="n">
-        <v>12.24767510780529</v>
+        <v>1.99024720501836</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.74220428064279</v>
+        <v>4.995608195604453</v>
       </c>
       <c r="D6" t="n">
-        <v>24.79810012874512</v>
+        <v>4.029691270921083</v>
       </c>
       <c r="E6" t="n">
-        <v>9.115993504248458</v>
+        <v>1.481348944440375</v>
       </c>
       <c r="F6" t="n">
-        <v>12.24767510780529</v>
+        <v>1.99024720501836</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>25.18710474438656</v>
+        <v>4.092904520962817</v>
       </c>
       <c r="D7" t="n">
-        <v>11.07795003955872</v>
+        <v>1.800166881428292</v>
       </c>
       <c r="E7" t="n">
-        <v>9.115993504248458</v>
+        <v>1.481348944440375</v>
       </c>
       <c r="F7" t="n">
-        <v>12.24767510780529</v>
+        <v>1.99024720501836</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>27.10454880947107</v>
+        <v>4.404489181539049</v>
       </c>
       <c r="D8" t="n">
-        <v>27.86684976123054</v>
+        <v>4.528363086199963</v>
       </c>
       <c r="E8" t="n">
-        <v>9.115993504248458</v>
+        <v>1.481348944440375</v>
       </c>
       <c r="F8" t="n">
-        <v>12.24767510780529</v>
+        <v>1.99024720501836</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>33.15659513088331</v>
+        <v>5.387946708768538</v>
       </c>
       <c r="D9" t="n">
-        <v>32.85882780735656</v>
+        <v>5.339559518695442</v>
       </c>
       <c r="E9" t="n">
-        <v>9.115993504248458</v>
+        <v>1.481348944440375</v>
       </c>
       <c r="F9" t="n">
-        <v>12.24767510780529</v>
+        <v>1.99024720501836</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>28.17966616423897</v>
+        <v>4.579195751688833</v>
       </c>
       <c r="D10" t="n">
-        <v>27.81479562574672</v>
+        <v>4.519904289183842</v>
       </c>
       <c r="E10" t="n">
-        <v>9.115993504248458</v>
+        <v>1.481348944440375</v>
       </c>
       <c r="F10" t="n">
-        <v>12.24767510780529</v>
+        <v>1.99024720501836</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>25.63457197292171</v>
+        <v>4.165617945599777</v>
       </c>
       <c r="D11" t="n">
-        <v>24.41030028837188</v>
+        <v>3.966673796860431</v>
       </c>
       <c r="E11" t="n">
-        <v>9.115993504248458</v>
+        <v>1.481348944440375</v>
       </c>
       <c r="F11" t="n">
-        <v>12.24767510780529</v>
+        <v>1.99024720501836</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>38.35741730420739</v>
+        <v>6.2330803119337</v>
       </c>
       <c r="D12" t="n">
-        <v>47.47054205872889</v>
+        <v>7.713963084543445</v>
       </c>
       <c r="E12" t="n">
-        <v>9.115993504248458</v>
+        <v>1.481348944440375</v>
       </c>
       <c r="F12" t="n">
-        <v>12.24767510780529</v>
+        <v>1.99024720501836</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>36.92978914144008</v>
+        <v>6.001090735484013</v>
       </c>
       <c r="D13" t="n">
-        <v>50.60483010487569</v>
+        <v>8.223284892042299</v>
       </c>
       <c r="E13" t="n">
-        <v>9.115993504248458</v>
+        <v>1.481348944440375</v>
       </c>
       <c r="F13" t="n">
-        <v>12.24767510780529</v>
+        <v>1.99024720501836</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>19.27527098437679</v>
+        <v>3.132231534961229</v>
       </c>
       <c r="D14" t="n">
-        <v>18.97559969662628</v>
+        <v>3.08353495070177</v>
       </c>
       <c r="E14" t="n">
-        <v>9.115993504248458</v>
+        <v>1.481348944440375</v>
       </c>
       <c r="F14" t="n">
-        <v>12.24767510780529</v>
+        <v>1.99024720501836</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>8.231881207442536</v>
+        <v>1.337680696209412</v>
       </c>
       <c r="D15" t="n">
-        <v>12.139043710489</v>
+        <v>1.972594602954463</v>
       </c>
       <c r="E15" t="n">
-        <v>9.115993504248458</v>
+        <v>1.481348944440375</v>
       </c>
       <c r="F15" t="n">
-        <v>12.24767510780529</v>
+        <v>1.99024720501836</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>15.32866370568537</v>
+        <v>2.490907852173873</v>
       </c>
       <c r="D16" t="n">
-        <v>10.81659573601018</v>
+        <v>1.757696807101654</v>
       </c>
       <c r="E16" t="n">
-        <v>9.115993504248458</v>
+        <v>1.481348944440375</v>
       </c>
       <c r="F16" t="n">
-        <v>12.24767510780529</v>
+        <v>1.99024720501836</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>13.48913824784912</v>
+        <v>2.191984965275482</v>
       </c>
       <c r="D17" t="n">
-        <v>11.82335451833673</v>
+        <v>1.921295109229719</v>
       </c>
       <c r="E17" t="n">
-        <v>9.115993504248458</v>
+        <v>1.481348944440375</v>
       </c>
       <c r="F17" t="n">
-        <v>12.24767510780529</v>
+        <v>1.99024720501836</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>32.93717473501673</v>
+        <v>5.35229089444022</v>
       </c>
       <c r="D18" t="n">
-        <v>32.9636571551613</v>
+        <v>5.356594287713712</v>
       </c>
       <c r="E18" t="n">
-        <v>9.115993504248458</v>
+        <v>1.481348944440375</v>
       </c>
       <c r="F18" t="n">
-        <v>12.24767510780529</v>
+        <v>1.99024720501836</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>11.8863880465765</v>
+        <v>1.931538057568681</v>
       </c>
       <c r="D19" t="n">
-        <v>34.72822999512142</v>
+        <v>5.643337374207231</v>
       </c>
       <c r="E19" t="n">
-        <v>9.115993504248458</v>
+        <v>1.481348944440375</v>
       </c>
       <c r="F19" t="n">
-        <v>12.24767510780529</v>
+        <v>1.99024720501836</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
